--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皇第 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -798,7 +665,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -844,7 +711,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -890,7 +757,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -936,7 +803,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1078,7 +945,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1124,7 +991,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1216,7 +1083,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-14</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1262,7 +1129,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1308,7 +1175,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1400,7 +1267,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1422,362 +1289,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>皇第 - 皇第 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>14 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>21&amp;22&amp;23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 6673呎 (4+房)
-$42,000万
-$62,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19&amp;20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 5515呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2848呎 (3房)
-$21,930万
-$77,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 2761呎 (3房)
-$21,930万
-$79,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 2761呎 (3房)
-$22,214万
-$80,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 2761呎 (3房)
-$20,561万
-$74,470/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11&amp;12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 4283呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10&amp;11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 2760呎 (2房)
-$20,000万
-$72,464/呎
-(20年-08月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>9&amp;10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr"/>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 2763呎 (2房)
-$18,500万
-$66,956/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>8&amp;9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 2846呎 (3房)
-$17,645万
-$62,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>7&amp;8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr"/>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 2763呎 (3房)
-$16,800万
-$60,803/呎
-(20年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>6&amp;7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 2760呎 (3房)
-$16,800万
-$60,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>5&amp;6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr"/>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 2849呎 (3房)
-$17,200万
-$60,372/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>3&amp;5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 3976呎 (3房)
-$21,200万
-$53,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>B&amp;G&amp;1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 4102呎 (3房)
-$28,714万
-$70,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 4075呎 (3房)
-$33,424万
-$82,022/呎
-(22年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="皇第" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1289,4 +1459,362 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>皇第 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>21&amp;22&amp;23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 6673呎 (4+房)
+$42000万
+$62,940/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19&amp;20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 5515呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2848呎 (3房)
+$21930万
+$77,000/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 2761呎 (3房)
+$21930万
+$79,426/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 2761呎 (3房)
+$22214万
+$80,458/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 2761呎 (3房)
+$20561万
+$74,470/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>11&amp;12</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr"/>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 4283呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>10&amp;11</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 2760呎 (2房)
+$20000万
+$72,464/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>9&amp;10</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 2763呎 (2房)
+$18500万
+$66,956/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>8&amp;9</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 2846呎 (3房)
+$17645万
+$62,000/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 2763呎 (3房)
+$16800万
+$60,803/呎
+(20年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>6&amp;7</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 2760呎 (3房)
+$16800万
+$60,870/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr"/>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 2849呎 (3房)
+$17200万
+$60,372/呎
+(20年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>3&amp;5</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 3976呎 (3房)
+$21200万
+$53,320/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>B&amp;G&amp;1&amp;2</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 4102呎 (3房)
+$28714万
+$70,000/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 4075呎 (3房)
+$33424万
+$82,022/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -750,6 +774,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -800,6 +844,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -846,6 +910,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -892,6 +976,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -938,6 +1042,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -984,6 +1108,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1034,6 +1178,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1080,6 +1244,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1126,6 +1310,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1172,6 +1376,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1218,6 +1442,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1264,6 +1508,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1310,6 +1574,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1356,6 +1640,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1706,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,13 +1772,33 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1574,7 +1918,7 @@
           <t>A | 6673呎 (4+房)
 $42000万
 $62,940/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -1606,7 +1950,7 @@
           <t>A | 2848呎 (3房)
 $21930万
 $77,000/呎
-(20年-06月)</t>
+(20年-06月-08日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -1622,7 +1966,7 @@
           <t>A | 2761呎 (3房)
 $21930万
 $79,426/呎
-(20年-06月)</t>
+(20年-06月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -1638,7 +1982,7 @@
           <t>A | 2761呎 (3房)
 $22214万
 $80,458/呎
-(20年-06月)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -1654,7 +1998,7 @@
           <t>A | 2761呎 (3房)
 $20561万
 $74,470/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -1686,7 +2030,7 @@
           <t>A | 2760呎 (2房)
 $20000万
 $72,464/呎
-(20年-08月)</t>
+(20年-08月-22日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -1703,7 +2047,7 @@
           <t>B | 2763呎 (2房)
 $18500万
 $66,956/呎
-(21年-09月)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -1718,7 +2062,7 @@
           <t>A | 2846呎 (3房)
 $17645万
 $62,000/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -1735,7 +2079,7 @@
           <t>B | 2763呎 (3房)
 $16800万
 $60,803/呎
-(20年-09月)</t>
+(20年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -1750,7 +2094,7 @@
           <t>A | 2760呎 (3房)
 $16800万
 $60,870/呎
-(20年-05月)</t>
+(20年-05月-14日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -1767,7 +2111,7 @@
           <t>B | 2849呎 (3房)
 $17200万
 $60,372/呎
-(20年-06月)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -1782,7 +2126,7 @@
           <t>A | 3976呎 (3房)
 $21200万
 $53,320/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -1798,7 +2142,7 @@
           <t>A | 4102呎 (3房)
 $28714万
 $70,000/呎
-(23年-02月)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -1806,7 +2150,7 @@
           <t>B | 4075呎 (3房)
 $33424万
 $82,022/呎
-(22年-05月)</t>
+(22年-05月-22日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -1918,7 +1918,7 @@
           <t>A | 6673呎 (4+房)
 $42000万
 $62,940/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
           <t>A | 2848呎 (3房)
 $21930万
 $77,000/呎
-(20年-06月-08日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
           <t>A | 2761呎 (3房)
 $21930万
 $79,426/呎
-(20年-06月-08日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
           <t>A | 2761呎 (3房)
 $22214万
 $80,458/呎
-(20年-06月-22日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
           <t>A | 2761呎 (3房)
 $20561万
 $74,470/呎
-(21年-08月-17日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
           <t>A | 2760呎 (2房)
 $20000万
 $72,464/呎
-(20年-08月-22日)</t>
+(20年-08月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
           <t>B | 2763呎 (2房)
 $18500万
 $66,956/呎
-(21年-09月-01日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
           <t>A | 2846呎 (3房)
 $17645万
 $62,000/呎
-(20年-02月-06日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
           <t>B | 2763呎 (3房)
 $16800万
 $60,803/呎
-(20年-09月-08日)</t>
+(20年-09月)</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
           <t>A | 2760呎 (3房)
 $16800万
 $60,870/呎
-(20年-05月-14日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
           <t>B | 2849呎 (3房)
 $17200万
 $60,372/呎
-(20年-06月-29日)</t>
+(20年-06月)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
           <t>A | 3976呎 (3房)
 $21200万
 $53,320/呎
-(24年-10月-21日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
           <t>A | 4102呎 (3房)
 $28714万
 $70,000/呎
-(23年-02月-06日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -2150,7 +2150,7 @@
           <t>B | 4075呎 (3房)
 $33424万
 $82,022/呎
-(22年-05月-22日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-皇第.xlsx
@@ -1918,7 +1918,7 @@
           <t>A | 6673呎 (4+房)
 $42000万
 $62,940/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
           <t>A | 2848呎 (3房)
 $21930万
 $77,000/呎
-(20年-06月)</t>
+(20年-06月-08日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
           <t>A | 2761呎 (3房)
 $21930万
 $79,426/呎
-(20年-06月)</t>
+(20年-06月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
           <t>A | 2761呎 (3房)
 $22214万
 $80,458/呎
-(20年-06月)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
           <t>A | 2761呎 (3房)
 $20561万
 $74,470/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
           <t>A | 2760呎 (2房)
 $20000万
 $72,464/呎
-(20年-08月)</t>
+(20年-08月-22日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
           <t>B | 2763呎 (2房)
 $18500万
 $66,956/呎
-(21年-09月)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
           <t>A | 2846呎 (3房)
 $17645万
 $62,000/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
           <t>B | 2763呎 (3房)
 $16800万
 $60,803/呎
-(20年-09月)</t>
+(20年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
           <t>A | 2760呎 (3房)
 $16800万
 $60,870/呎
-(20年-05月)</t>
+(20年-05月-14日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
           <t>B | 2849呎 (3房)
 $17200万
 $60,372/呎
-(20年-06月)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
           <t>A | 3976呎 (3房)
 $21200万
 $53,320/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
           <t>A | 4102呎 (3房)
 $28714万
 $70,000/呎
-(23年-02月)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -2150,7 +2150,7 @@
           <t>B | 4075呎 (3房)
 $33424万
 $82,022/呎
-(22年-05月)</t>
+(22年-05月-22日)</t>
         </is>
       </c>
     </row>
